--- a/docs/API명세서_v1.0_CKD.xlsx
+++ b/docs/API명세서_v1.0_CKD.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="33" min="1" max="1"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="B5" s="45" t="inlineStr">
         <is>
-          <t>api/v1/auth/register</t>
+          <t>api/v1/auth/signup</t>
         </is>
       </c>
       <c r="C5" s="44" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="B9" s="45" t="inlineStr">
         <is>
-          <t>api/v1/auth/refresh</t>
+          <t>api/v1/auth/token/refresh</t>
         </is>
       </c>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D9" s="44" t="inlineStr">
         <is>
-          <t>JWT 토큰 재발급 (Refresh Token Rotate, REQ-AUTH-006/REQ-SEC-003)</t>
+          <t>JWT 액세스 토큰 갱신 (Refresh 쿠키 기반)</t>
         </is>
       </c>
       <c r="E9" s="46" t="inlineStr"/>
@@ -1285,17 +1285,17 @@
       </c>
       <c r="B10" s="45" t="inlineStr">
         <is>
-          <t>api/v1/auth/oauth/kakao</t>
+          <t>api/v1/auth/kakao/login</t>
         </is>
       </c>
       <c r="C10" s="44" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D10" s="44" t="inlineStr">
         <is>
-          <t>카카오 OAuth 로그인 (P1, REQ-AUTH-008)</t>
+          <t>카카오 OAuth 시작 (인가 코드 흐름)</t>
         </is>
       </c>
       <c r="E10" s="46" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B13" s="45" t="inlineStr">
         <is>
-          <t>api/v1/me</t>
+          <t>api/v1/users/me</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B15" s="45" t="inlineStr">
         <is>
-          <t>api/v1/checkups/ocr</t>
+          <t>api/v1/health-checks/ocr</t>
         </is>
       </c>
       <c r="C15" s="44" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B16" s="45" t="inlineStr">
         <is>
-          <t>api/v1/checkups/ocr/{upload_id}</t>
+          <t>api/v1/health-checks/ocr/{upload_id}</t>
         </is>
       </c>
       <c r="C16" s="44" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B17" s="45" t="inlineStr">
         <is>
-          <t>api/v1/checkups</t>
+          <t>api/v1/health-checks</t>
         </is>
       </c>
       <c r="C17" s="44" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B18" s="45" t="inlineStr">
         <is>
-          <t>api/v1/checkups</t>
+          <t>api/v1/health-checks</t>
         </is>
       </c>
       <c r="C18" s="44" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B19" s="45" t="inlineStr">
         <is>
-          <t>api/v1/checkups/{checkup_id}</t>
+          <t>api/v1/health-checks/{id}</t>
         </is>
       </c>
       <c r="C19" s="44" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B20" s="45" t="inlineStr">
         <is>
-          <t>api/v1/surveys/lifestyle</t>
+          <t>api/v1/lifestyle-surveys</t>
         </is>
       </c>
       <c r="C20" s="44" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B26" s="45" t="inlineStr">
         <is>
-          <t>api/v1/predictions/egfr-trend</t>
+          <t>api/v1/dashboard/egfr-trend</t>
         </is>
       </c>
       <c r="C26" s="44" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D26" s="44" t="inlineStr">
         <is>
-          <t>eGFR 추세 조회 (REQ-DASH-001 ②)</t>
+          <t>eGFR 추세 (대시보드 카테고리)</t>
         </is>
       </c>
       <c r="E26" s="46" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B29" s="45" t="inlineStr">
         <is>
-          <t>api/v1/challenges/assign</t>
+          <t>api/v1/user-challenges</t>
         </is>
       </c>
       <c r="C29" s="44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>챌린지 트랙·스테이지 자동 배정 (A: G1·G2 / B: G3·G4, REQ-CHAL-001)</t>
+          <t>챌린지 참여 (자동 배정 대신 사용자 선택)</t>
         </is>
       </c>
       <c r="E29" s="46" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B30" s="45" t="inlineStr">
         <is>
-          <t>api/v1/challenges/{user_challenge_id}/checkin</t>
+          <t>api/v1/user-challenges/{user_challenge_id}/checkin</t>
         </is>
       </c>
       <c r="C30" s="44" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="C45" s="44" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D45" s="44" t="inlineStr">
@@ -6424,6 +6424,567 @@
       </c>
       <c r="P66" s="45" t="n"/>
       <c r="Q66" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B67" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/auth/kakao/callback</t>
+        </is>
+      </c>
+      <c r="C67" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D67" s="44" t="inlineStr">
+        <is>
+          <t>카카오 OAuth 콜백 (인가 코드 → JWT)</t>
+        </is>
+      </c>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F67" s="46" t="n"/>
+      <c r="G67" s="46" t="n"/>
+      <c r="H67" s="46" t="n"/>
+      <c r="I67" s="45" t="n"/>
+      <c r="J67" s="45" t="n"/>
+      <c r="K67" s="47" t="inlineStr">
+        <is>
+          <t>200: OK</t>
+        </is>
+      </c>
+      <c r="L67" s="47" t="n"/>
+      <c r="M67" s="47" t="n"/>
+      <c r="N67" s="47" t="n"/>
+      <c r="O67" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P67" s="45" t="n"/>
+      <c r="Q67" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B68" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/auth/google/login</t>
+        </is>
+      </c>
+      <c r="C68" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D68" s="44" t="inlineStr">
+        <is>
+          <t>구글 OAuth 시작 (P1)</t>
+        </is>
+      </c>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F68" s="46" t="n"/>
+      <c r="G68" s="46" t="n"/>
+      <c r="H68" s="46" t="n"/>
+      <c r="I68" s="45" t="n"/>
+      <c r="J68" s="45" t="n"/>
+      <c r="K68" s="47" t="inlineStr">
+        <is>
+          <t>200: OK</t>
+        </is>
+      </c>
+      <c r="L68" s="47" t="n"/>
+      <c r="M68" s="47" t="n"/>
+      <c r="N68" s="47" t="n"/>
+      <c r="O68" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P68" s="45" t="n"/>
+      <c r="Q68" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B69" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/auth/google/callback</t>
+        </is>
+      </c>
+      <c r="C69" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D69" s="44" t="inlineStr">
+        <is>
+          <t>구글 OAuth 콜백 (P1)</t>
+        </is>
+      </c>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F69" s="46" t="n"/>
+      <c r="G69" s="46" t="n"/>
+      <c r="H69" s="46" t="n"/>
+      <c r="I69" s="45" t="n"/>
+      <c r="J69" s="45" t="n"/>
+      <c r="K69" s="47" t="inlineStr">
+        <is>
+          <t>200: OK</t>
+        </is>
+      </c>
+      <c r="L69" s="47" t="n"/>
+      <c r="M69" s="47" t="n"/>
+      <c r="N69" s="47" t="n"/>
+      <c r="O69" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P69" s="45" t="n"/>
+      <c r="Q69" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B70" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/users/me</t>
+        </is>
+      </c>
+      <c r="C70" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D70" s="44" t="inlineStr">
+        <is>
+          <t>내 정보 조회</t>
+        </is>
+      </c>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F70" s="46" t="n"/>
+      <c r="G70" s="46" t="n"/>
+      <c r="H70" s="46" t="n"/>
+      <c r="I70" s="45" t="n"/>
+      <c r="J70" s="45" t="n"/>
+      <c r="K70" s="47" t="inlineStr">
+        <is>
+          <t>200: {"id": int, "email": str, "name": str, ...}</t>
+        </is>
+      </c>
+      <c r="L70" s="47" t="n"/>
+      <c r="M70" s="47" t="n"/>
+      <c r="N70" s="47" t="n"/>
+      <c r="O70" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P70" s="45" t="n"/>
+      <c r="Q70" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B71" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/users/me</t>
+        </is>
+      </c>
+      <c r="C71" s="44" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D71" s="44" t="inlineStr">
+        <is>
+          <t>내 정보 수정</t>
+        </is>
+      </c>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F71" s="46" t="n"/>
+      <c r="G71" s="46" t="n"/>
+      <c r="H71" s="46" t="n"/>
+      <c r="I71" s="45" t="n"/>
+      <c r="J71" s="45" t="n"/>
+      <c r="K71" s="47" t="inlineStr">
+        <is>
+          <t>200: 수정된 사용자 정보</t>
+        </is>
+      </c>
+      <c r="L71" s="47" t="n"/>
+      <c r="M71" s="47" t="n"/>
+      <c r="N71" s="47" t="n"/>
+      <c r="O71" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P71" s="45" t="n"/>
+      <c r="Q71" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B72" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/user-challenges</t>
+        </is>
+      </c>
+      <c r="C72" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D72" s="44" t="inlineStr">
+        <is>
+          <t>내 챌린지 목록</t>
+        </is>
+      </c>
+      <c r="E72" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F72" s="46" t="n"/>
+      <c r="G72" s="46" t="n"/>
+      <c r="H72" s="46" t="n"/>
+      <c r="I72" s="45" t="n"/>
+      <c r="J72" s="45" t="n"/>
+      <c r="K72" s="47" t="inlineStr">
+        <is>
+          <t>200: {"total": int, "items": [UserChallenge]}</t>
+        </is>
+      </c>
+      <c r="L72" s="47" t="n"/>
+      <c r="M72" s="47" t="n"/>
+      <c r="N72" s="47" t="n"/>
+      <c r="O72" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P72" s="45" t="n"/>
+      <c r="Q72" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B73" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/challenges</t>
+        </is>
+      </c>
+      <c r="C73" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D73" s="44" t="inlineStr">
+        <is>
+          <t>챌린지 카탈로그 조회 (그룹별)</t>
+        </is>
+      </c>
+      <c r="E73" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F73" s="46" t="n"/>
+      <c r="G73" s="46" t="n"/>
+      <c r="H73" s="46" t="n"/>
+      <c r="I73" s="45" t="n"/>
+      <c r="J73" s="45" t="n"/>
+      <c r="K73" s="47" t="inlineStr">
+        <is>
+          <t>200: {"total": int, "items": [Challenge]}</t>
+        </is>
+      </c>
+      <c r="L73" s="47" t="n"/>
+      <c r="M73" s="47" t="n"/>
+      <c r="N73" s="47" t="n"/>
+      <c r="O73" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P73" s="45" t="n"/>
+      <c r="Q73" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B74" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/lifestyle-surveys</t>
+        </is>
+      </c>
+      <c r="C74" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D74" s="44" t="inlineStr">
+        <is>
+          <t>생활습관 설문 이력</t>
+        </is>
+      </c>
+      <c r="E74" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F74" s="46" t="n"/>
+      <c r="G74" s="46" t="n"/>
+      <c r="H74" s="46" t="n"/>
+      <c r="I74" s="45" t="n"/>
+      <c r="J74" s="45" t="n"/>
+      <c r="K74" s="47" t="inlineStr">
+        <is>
+          <t>200: {"total": int, "items": [LifestyleSurvey]}</t>
+        </is>
+      </c>
+      <c r="L74" s="47" t="n"/>
+      <c r="M74" s="47" t="n"/>
+      <c r="N74" s="47" t="n"/>
+      <c r="O74" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P74" s="45" t="n"/>
+      <c r="Q74" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B75" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/lifestyle-surveys/{id}</t>
+        </is>
+      </c>
+      <c r="C75" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D75" s="44" t="inlineStr">
+        <is>
+          <t>생활습관 설문 단건 조회</t>
+        </is>
+      </c>
+      <c r="E75" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F75" s="46" t="n"/>
+      <c r="G75" s="46" t="n"/>
+      <c r="H75" s="46" t="n"/>
+      <c r="I75" s="45" t="n"/>
+      <c r="J75" s="45" t="n"/>
+      <c r="K75" s="47" t="inlineStr">
+        <is>
+          <t>200: LifestyleSurveyResponse</t>
+        </is>
+      </c>
+      <c r="L75" s="47" t="n"/>
+      <c r="M75" s="47" t="n"/>
+      <c r="N75" s="47" t="n"/>
+      <c r="O75" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P75" s="45" t="n"/>
+      <c r="Q75" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B76" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/diet-surveys</t>
+        </is>
+      </c>
+      <c r="C76" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D76" s="44" t="inlineStr">
+        <is>
+          <t>식이 설문 이력</t>
+        </is>
+      </c>
+      <c r="E76" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F76" s="46" t="n"/>
+      <c r="G76" s="46" t="n"/>
+      <c r="H76" s="46" t="n"/>
+      <c r="I76" s="45" t="n"/>
+      <c r="J76" s="45" t="n"/>
+      <c r="K76" s="47" t="inlineStr">
+        <is>
+          <t>200: {"total": int, "items": [DietSurvey]}</t>
+        </is>
+      </c>
+      <c r="L76" s="47" t="n"/>
+      <c r="M76" s="47" t="n"/>
+      <c r="N76" s="47" t="n"/>
+      <c r="O76" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P76" s="45" t="n"/>
+      <c r="Q76" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B77" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/notifications/read-all</t>
+        </is>
+      </c>
+      <c r="C77" s="44" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D77" s="44" t="inlineStr">
+        <is>
+          <t>알림 전체 읽음 처리</t>
+        </is>
+      </c>
+      <c r="E77" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F77" s="46" t="n"/>
+      <c r="G77" s="46" t="n"/>
+      <c r="H77" s="46" t="n"/>
+      <c r="I77" s="45" t="n"/>
+      <c r="J77" s="45" t="n"/>
+      <c r="K77" s="47" t="inlineStr">
+        <is>
+          <t>200: {"updated": int}</t>
+        </is>
+      </c>
+      <c r="L77" s="47" t="n"/>
+      <c r="M77" s="47" t="n"/>
+      <c r="N77" s="47" t="n"/>
+      <c r="O77" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P77" s="45" t="n"/>
+      <c r="Q77" s="44" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/docs/API명세서_v1.0_CKD.xlsx
+++ b/docs/API명세서_v1.0_CKD.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="33" min="1" max="1"/>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="D57" s="44" t="inlineStr">
         <is>
-          <t>임시 비밀번호 발급 (REQ-AUTH-011, 임시 구현·교체 예정)</t>
+          <t>임시 비밀번호 발급 (REQ-AUTH-011, 임시 구현·교체 예정) [DEPRECATED: 새 2단계 흐름 권장]</t>
         </is>
       </c>
       <c r="E57" s="46" t="inlineStr">
@@ -5802,45 +5802,161 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B58" s="45" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>api/v1/auth/password-reset/request</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>비밀번호 재설정 코드 발급 (REQ-AUTH-C, Rate Limit 5회/분, EMAIL_MODE=demo|production)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{
+  "email": {type: str, required: true, format: "RFC 5322"}
+}</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>{
+  "sent": bool,
+  "mode": "demo"|"production",
+  "demo_code": str|null,
+  "expires_in_seconds": int
+}</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>코드 발송 성공 (demo면 demo_code에 6자리 코드 노출)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>api/v1/auth/password-reset/verify</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>코드 검증 + 임시 비밀번호 발급 (Rate Limit 10회/분, 5회 실패 시 코드 무효화)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{
+  "email": {type: str, required: true},
+  "code":  {type: str, required: true, format: "6자리 숫자"}
+}</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>{
+  "temp_password": str
+}</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>발급된 임시 비밀번호로 즉시 로그인 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B60" s="45" t="inlineStr">
         <is>
           <t>api/v1/gamification/eggs</t>
         </is>
       </c>
-      <c r="C58" s="44" t="inlineStr">
+      <c r="C60" s="44" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D58" s="44" t="inlineStr">
+      <c r="D60" s="44" t="inlineStr">
         <is>
           <t>현재 알 상태 조회 (REQ-CHAL-004)</t>
         </is>
       </c>
-      <c r="E58" s="46" t="inlineStr">
+      <c r="E60" s="46" t="inlineStr">
         <is>
           <t>{
   "Authorization": "Bearer &lt;token&gt;"
 }</t>
         </is>
       </c>
-      <c r="F58" s="46" t="inlineStr">
+      <c r="F60" s="46" t="inlineStr">
         <is>
           <t>{
   "Authorization": "Bearer eyJ..."
 }</t>
         </is>
       </c>
-      <c r="G58" s="46" t="n"/>
-      <c r="H58" s="46" t="n"/>
-      <c r="I58" s="45" t="n"/>
-      <c r="J58" s="45" t="n"/>
-      <c r="K58" s="47" t="inlineStr">
+      <c r="G60" s="46" t="n"/>
+      <c r="H60" s="46" t="n"/>
+      <c r="I60" s="45" t="n"/>
+      <c r="J60" s="45" t="n"/>
+      <c r="K60" s="47" t="inlineStr">
         <is>
           <t>200: {
   "egg_no": int,
@@ -5852,7 +5968,7 @@
 }</t>
         </is>
       </c>
-      <c r="L58" s="47" t="inlineStr">
+      <c r="L60" s="47" t="inlineStr">
         <is>
           <t>200: {
   "egg_no": 1,
@@ -5863,157 +5979,19 @@
 }</t>
         </is>
       </c>
-      <c r="M58" s="47" t="inlineStr">
+      <c r="M60" s="47" t="inlineStr">
         <is>
           <t>401: {"error_detail": str}</t>
         </is>
       </c>
-      <c r="N58" s="47" t="inlineStr">
+      <c r="N60" s="47" t="inlineStr">
         <is>
           <t>401: 인증 필요</t>
         </is>
       </c>
-      <c r="O58" s="45" t="inlineStr">
+      <c r="O60" s="45" t="inlineStr">
         <is>
           <t>{200: OK, 401: Unauthorized}</t>
-        </is>
-      </c>
-      <c r="P58" s="45" t="n"/>
-      <c r="Q58" s="44" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="44" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B59" s="45" t="inlineStr">
-        <is>
-          <t>api/v1/gamification/eggs/history</t>
-        </is>
-      </c>
-      <c r="C59" s="44" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D59" s="44" t="inlineStr">
-        <is>
-          <t>부화 이력 조회 (전설 5% 포함)</t>
-        </is>
-      </c>
-      <c r="E59" s="46" t="inlineStr">
-        <is>
-          <t>{"Authorization": str}</t>
-        </is>
-      </c>
-      <c r="F59" s="46" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="G59" s="46" t="n"/>
-      <c r="H59" s="46" t="n"/>
-      <c r="I59" s="45" t="n"/>
-      <c r="J59" s="45" t="n"/>
-      <c r="K59" s="47" t="inlineStr">
-        <is>
-          <t>200: {
-  "total": int,
-  "legendary_count": int,
-  "items": [{egg_no, is_legendary, hatched_at}]
-}</t>
-        </is>
-      </c>
-      <c r="L59" s="47" t="inlineStr">
-        <is>
-          <t>{
-  "total": 2, "legendary_count": 1,
-  "items": [...]
-}</t>
-        </is>
-      </c>
-      <c r="M59" s="47" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="N59" s="47" t="inlineStr"/>
-      <c r="O59" s="45" t="inlineStr">
-        <is>
-          <t>{200: OK, 401}</t>
-        </is>
-      </c>
-      <c r="P59" s="45" t="n"/>
-      <c r="Q59" s="44" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="44" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B60" s="45" t="inlineStr">
-        <is>
-          <t>api/v1/gamification/mascot</t>
-        </is>
-      </c>
-      <c r="C60" s="44" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D60" s="44" t="inlineStr">
-        <is>
-          <t>캐릭터 + 충전 모드 통합 조회</t>
-        </is>
-      </c>
-      <c r="E60" s="46" t="inlineStr">
-        <is>
-          <t>{"Authorization": str}</t>
-        </is>
-      </c>
-      <c r="F60" s="46" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="G60" s="46" t="n"/>
-      <c r="H60" s="46" t="n"/>
-      <c r="I60" s="45" t="n"/>
-      <c r="J60" s="45" t="n"/>
-      <c r="K60" s="47" t="inlineStr">
-        <is>
-          <t>200: {
-  "current_egg": EggResponse,
-  "charge_mode": ChargeModeResponse,
-  "legendary_unlocked": bool,
-  "skin_active": ItemCode|null
-}</t>
-        </is>
-      </c>
-      <c r="L60" s="47" t="inlineStr">
-        <is>
-          <t>...</t>
-        </is>
-      </c>
-      <c r="M60" s="47" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="N60" s="47" t="inlineStr"/>
-      <c r="O60" s="45" t="inlineStr">
-        <is>
-          <t>{200, 401}</t>
         </is>
       </c>
       <c r="P60" s="45" t="n"/>
@@ -6031,7 +6009,7 @@
       </c>
       <c r="B61" s="45" t="inlineStr">
         <is>
-          <t>api/v1/gamification/charge-mode</t>
+          <t>api/v1/gamification/eggs/history</t>
         </is>
       </c>
       <c r="C61" s="44" t="inlineStr">
@@ -6041,7 +6019,7 @@
       </c>
       <c r="D61" s="44" t="inlineStr">
         <is>
-          <t>쉬어가기 모드 상태 조회</t>
+          <t>부화 이력 조회 (전설 5% 포함)</t>
         </is>
       </c>
       <c r="E61" s="46" t="inlineStr">
@@ -6061,15 +6039,18 @@
       <c r="K61" s="47" t="inlineStr">
         <is>
           <t>200: {
-  "is_active": bool,
-  "entered_at": datetime|null,
-  "days_since_last_checkin": int|null
+  "total": int,
+  "legendary_count": int,
+  "items": [{egg_no, is_legendary, hatched_at}]
 }</t>
         </is>
       </c>
       <c r="L61" s="47" t="inlineStr">
         <is>
-          <t>...</t>
+          <t>{
+  "total": 2, "legendary_count": 1,
+  "items": [...]
+}</t>
         </is>
       </c>
       <c r="M61" s="47" t="inlineStr">
@@ -6080,7 +6061,7 @@
       <c r="N61" s="47" t="inlineStr"/>
       <c r="O61" s="45" t="inlineStr">
         <is>
-          <t>{200, 401}</t>
+          <t>{200: OK, 401}</t>
         </is>
       </c>
       <c r="P61" s="45" t="n"/>
@@ -6098,17 +6079,17 @@
       </c>
       <c r="B62" s="45" t="inlineStr">
         <is>
-          <t>api/v1/gamification/charge-mode/exit</t>
+          <t>api/v1/gamification/mascot</t>
         </is>
       </c>
       <c r="C62" s="44" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D62" s="44" t="inlineStr">
         <is>
-          <t>쉬어가기 모드 명시적 탈출 (UI 버튼용)</t>
+          <t>캐릭터 + 충전 모드 통합 조회</t>
         </is>
       </c>
       <c r="E62" s="46" t="inlineStr">
@@ -6123,19 +6104,16 @@
       </c>
       <c r="G62" s="46" t="n"/>
       <c r="H62" s="46" t="n"/>
-      <c r="I62" s="45" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J62" s="45" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
+      <c r="I62" s="45" t="n"/>
+      <c r="J62" s="45" t="n"/>
       <c r="K62" s="47" t="inlineStr">
         <is>
-          <t>200: ChargeModeResponse</t>
+          <t>200: {
+  "current_egg": EggResponse,
+  "charge_mode": ChargeModeResponse,
+  "legendary_unlocked": bool,
+  "skin_active": ItemCode|null
+}</t>
         </is>
       </c>
       <c r="L62" s="47" t="inlineStr">
@@ -6145,14 +6123,13 @@
       </c>
       <c r="M62" s="47" t="inlineStr">
         <is>
-          <t>400: {"error_detail": "이미 정상 모드"}
-401</t>
+          <t>401</t>
         </is>
       </c>
       <c r="N62" s="47" t="inlineStr"/>
       <c r="O62" s="45" t="inlineStr">
         <is>
-          <t>{200, 400, 401}</t>
+          <t>{200, 401}</t>
         </is>
       </c>
       <c r="P62" s="45" t="n"/>
@@ -6170,7 +6147,7 @@
       </c>
       <c r="B63" s="45" t="inlineStr">
         <is>
-          <t>api/v1/inventory</t>
+          <t>api/v1/gamification/charge-mode</t>
         </is>
       </c>
       <c r="C63" s="44" t="inlineStr">
@@ -6180,7 +6157,7 @@
       </c>
       <c r="D63" s="44" t="inlineStr">
         <is>
-          <t>보유 아이템 목록 (REQ-CHAL-011)</t>
+          <t>쉬어가기 모드 상태 조회</t>
         </is>
       </c>
       <c r="E63" s="46" t="inlineStr">
@@ -6199,7 +6176,11 @@
       <c r="J63" s="45" t="n"/>
       <c r="K63" s="47" t="inlineStr">
         <is>
-          <t>200: {"total": int, "items": [{item_code, quantity, acquired_at}]}</t>
+          <t>200: {
+  "is_active": bool,
+  "entered_at": datetime|null,
+  "days_since_last_checkin": int|null
+}</t>
         </is>
       </c>
       <c r="L63" s="47" t="inlineStr">
@@ -6233,17 +6214,17 @@
       </c>
       <c r="B64" s="45" t="inlineStr">
         <is>
-          <t>api/v1/points/balance</t>
+          <t>api/v1/gamification/charge-mode/exit</t>
         </is>
       </c>
       <c r="C64" s="44" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D64" s="44" t="inlineStr">
         <is>
-          <t>포인트 잔액 + 평생 누적 (REQ-CHAL-010)</t>
+          <t>쉬어가기 모드 명시적 탈출 (UI 버튼용)</t>
         </is>
       </c>
       <c r="E64" s="46" t="inlineStr">
@@ -6258,31 +6239,36 @@
       </c>
       <c r="G64" s="46" t="n"/>
       <c r="H64" s="46" t="n"/>
-      <c r="I64" s="45" t="n"/>
-      <c r="J64" s="45" t="n"/>
+      <c r="I64" s="45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J64" s="45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
       <c r="K64" s="47" t="inlineStr">
         <is>
-          <t>200: {
-  "balance": int,
-  "lifetime_earned": int,
-  "lifetime_spent": int
-}</t>
+          <t>200: ChargeModeResponse</t>
         </is>
       </c>
       <c r="L64" s="47" t="inlineStr">
         <is>
-          <t>{"balance": 1800, "lifetime_earned": 2400, "lifetime_spent": 600}</t>
+          <t>...</t>
         </is>
       </c>
       <c r="M64" s="47" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>400: {"error_detail": "이미 정상 모드"}
+401</t>
         </is>
       </c>
       <c r="N64" s="47" t="inlineStr"/>
       <c r="O64" s="45" t="inlineStr">
         <is>
-          <t>{200, 401}</t>
+          <t>{200, 400, 401}</t>
         </is>
       </c>
       <c r="P64" s="45" t="n"/>
@@ -6300,7 +6286,7 @@
       </c>
       <c r="B65" s="45" t="inlineStr">
         <is>
-          <t>api/v1/points/transactions</t>
+          <t>api/v1/inventory</t>
         </is>
       </c>
       <c r="C65" s="44" t="inlineStr">
@@ -6310,7 +6296,7 @@
       </c>
       <c r="D65" s="44" t="inlineStr">
         <is>
-          <t>포인트 적립·소비 이력 (페이지네이션)</t>
+          <t>보유 아이템 목록 (REQ-CHAL-011)</t>
         </is>
       </c>
       <c r="E65" s="46" t="inlineStr">
@@ -6320,7 +6306,7 @@
       </c>
       <c r="F65" s="46" t="inlineStr">
         <is>
-          <t>limit=20&amp;offset=0</t>
+          <t>...</t>
         </is>
       </c>
       <c r="G65" s="46" t="n"/>
@@ -6329,7 +6315,7 @@
       <c r="J65" s="45" t="n"/>
       <c r="K65" s="47" t="inlineStr">
         <is>
-          <t>200: {"total": int, "items": [{id, amount, reason, extra, created_at}]}</t>
+          <t>200: {"total": int, "items": [{item_code, quantity, acquired_at}]}</t>
         </is>
       </c>
       <c r="L65" s="47" t="inlineStr">
@@ -6363,17 +6349,17 @@
       </c>
       <c r="B66" s="45" t="inlineStr">
         <is>
-          <t>api/v1/points/purchase</t>
+          <t>api/v1/points/balance</t>
         </is>
       </c>
       <c r="C66" s="44" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D66" s="44" t="inlineStr">
         <is>
-          <t>아이템 구매 (보호권 2개 캡, 스킨 중복 차단)</t>
+          <t>포인트 잔액 + 평생 누적 (REQ-CHAL-010)</t>
         </is>
       </c>
       <c r="E66" s="46" t="inlineStr">
@@ -6388,38 +6374,31 @@
       </c>
       <c r="G66" s="46" t="n"/>
       <c r="H66" s="46" t="n"/>
-      <c r="I66" s="45" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J66" s="45" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
+      <c r="I66" s="45" t="n"/>
+      <c r="J66" s="45" t="n"/>
       <c r="K66" s="47" t="inlineStr">
         <is>
-          <t>200: {"item_code": str, "new_quantity": int, "spent": int, "new_balance": int}</t>
+          <t>200: {
+  "balance": int,
+  "lifetime_earned": int,
+  "lifetime_spent": int
+}</t>
         </is>
       </c>
       <c r="L66" s="47" t="inlineStr">
         <is>
-          <t>{"item_code": "PROTECT", "new_quantity": 1, "spent": 500, "new_balance": 1300}</t>
+          <t>{"balance": 1800, "lifetime_earned": 2400, "lifetime_spent": 600}</t>
         </is>
       </c>
       <c r="M66" s="47" t="inlineStr">
         <is>
-          <t>400: 포인트 부족
-409: 이미 보유
-409: 보호권 최대 2개
-401</t>
+          <t>401</t>
         </is>
       </c>
       <c r="N66" s="47" t="inlineStr"/>
       <c r="O66" s="45" t="inlineStr">
         <is>
-          <t>{200, 400, 401, 409}</t>
+          <t>{200, 401}</t>
         </is>
       </c>
       <c r="P66" s="45" t="n"/>
@@ -6437,7 +6416,7 @@
       </c>
       <c r="B67" s="45" t="inlineStr">
         <is>
-          <t>api/v1/auth/kakao/callback</t>
+          <t>api/v1/points/transactions</t>
         </is>
       </c>
       <c r="C67" s="44" t="inlineStr">
@@ -6447,27 +6426,39 @@
       </c>
       <c r="D67" s="44" t="inlineStr">
         <is>
-          <t>카카오 OAuth 콜백 (인가 코드 → JWT)</t>
+          <t>포인트 적립·소비 이력 (페이지네이션)</t>
         </is>
       </c>
       <c r="E67" s="46" t="inlineStr">
         <is>
-          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
-        </is>
-      </c>
-      <c r="F67" s="46" t="n"/>
+          <t>{"Authorization": str}</t>
+        </is>
+      </c>
+      <c r="F67" s="46" t="inlineStr">
+        <is>
+          <t>limit=20&amp;offset=0</t>
+        </is>
+      </c>
       <c r="G67" s="46" t="n"/>
       <c r="H67" s="46" t="n"/>
       <c r="I67" s="45" t="n"/>
       <c r="J67" s="45" t="n"/>
       <c r="K67" s="47" t="inlineStr">
         <is>
-          <t>200: OK</t>
-        </is>
-      </c>
-      <c r="L67" s="47" t="n"/>
-      <c r="M67" s="47" t="n"/>
-      <c r="N67" s="47" t="n"/>
+          <t>200: {"total": int, "items": [{id, amount, reason, extra, created_at}]}</t>
+        </is>
+      </c>
+      <c r="L67" s="47" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="M67" s="47" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="N67" s="47" t="inlineStr"/>
       <c r="O67" s="45" t="inlineStr">
         <is>
           <t>{200, 401}</t>
@@ -6488,40 +6479,63 @@
       </c>
       <c r="B68" s="45" t="inlineStr">
         <is>
-          <t>api/v1/auth/google/login</t>
+          <t>api/v1/points/purchase</t>
         </is>
       </c>
       <c r="C68" s="44" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="D68" s="44" t="inlineStr">
         <is>
-          <t>구글 OAuth 시작 (P1)</t>
+          <t>아이템 구매 (보호권 2개 캡, 스킨 중복 차단)</t>
         </is>
       </c>
       <c r="E68" s="46" t="inlineStr">
         <is>
-          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
-        </is>
-      </c>
-      <c r="F68" s="46" t="n"/>
+          <t>{"Authorization": str}</t>
+        </is>
+      </c>
+      <c r="F68" s="46" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
       <c r="G68" s="46" t="n"/>
       <c r="H68" s="46" t="n"/>
-      <c r="I68" s="45" t="n"/>
-      <c r="J68" s="45" t="n"/>
+      <c r="I68" s="45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J68" s="45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
       <c r="K68" s="47" t="inlineStr">
         <is>
-          <t>200: OK</t>
-        </is>
-      </c>
-      <c r="L68" s="47" t="n"/>
-      <c r="M68" s="47" t="n"/>
-      <c r="N68" s="47" t="n"/>
+          <t>200: {"item_code": str, "new_quantity": int, "spent": int, "new_balance": int}</t>
+        </is>
+      </c>
+      <c r="L68" s="47" t="inlineStr">
+        <is>
+          <t>{"item_code": "PROTECT", "new_quantity": 1, "spent": 500, "new_balance": 1300}</t>
+        </is>
+      </c>
+      <c r="M68" s="47" t="inlineStr">
+        <is>
+          <t>400: 포인트 부족
+409: 이미 보유
+409: 보호권 최대 2개
+401</t>
+        </is>
+      </c>
+      <c r="N68" s="47" t="inlineStr"/>
       <c r="O68" s="45" t="inlineStr">
         <is>
-          <t>{200, 401}</t>
+          <t>{200, 400, 401, 409}</t>
         </is>
       </c>
       <c r="P68" s="45" t="n"/>
@@ -6539,7 +6553,7 @@
       </c>
       <c r="B69" s="45" t="inlineStr">
         <is>
-          <t>api/v1/auth/google/callback</t>
+          <t>api/v1/auth/kakao/callback</t>
         </is>
       </c>
       <c r="C69" s="44" t="inlineStr">
@@ -6549,7 +6563,7 @@
       </c>
       <c r="D69" s="44" t="inlineStr">
         <is>
-          <t>구글 OAuth 콜백 (P1)</t>
+          <t>카카오 OAuth 콜백 (인가 코드 → JWT)</t>
         </is>
       </c>
       <c r="E69" s="46" t="inlineStr">
@@ -6590,7 +6604,7 @@
       </c>
       <c r="B70" s="45" t="inlineStr">
         <is>
-          <t>api/v1/users/me</t>
+          <t>api/v1/auth/google/login</t>
         </is>
       </c>
       <c r="C70" s="44" t="inlineStr">
@@ -6600,7 +6614,7 @@
       </c>
       <c r="D70" s="44" t="inlineStr">
         <is>
-          <t>내 정보 조회</t>
+          <t>구글 OAuth 시작 (P1)</t>
         </is>
       </c>
       <c r="E70" s="46" t="inlineStr">
@@ -6615,7 +6629,7 @@
       <c r="J70" s="45" t="n"/>
       <c r="K70" s="47" t="inlineStr">
         <is>
-          <t>200: {"id": int, "email": str, "name": str, ...}</t>
+          <t>200: OK</t>
         </is>
       </c>
       <c r="L70" s="47" t="n"/>
@@ -6641,17 +6655,17 @@
       </c>
       <c r="B71" s="45" t="inlineStr">
         <is>
-          <t>api/v1/users/me</t>
+          <t>api/v1/auth/google/callback</t>
         </is>
       </c>
       <c r="C71" s="44" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D71" s="44" t="inlineStr">
         <is>
-          <t>내 정보 수정</t>
+          <t>구글 OAuth 콜백 (P1)</t>
         </is>
       </c>
       <c r="E71" s="46" t="inlineStr">
@@ -6666,7 +6680,7 @@
       <c r="J71" s="45" t="n"/>
       <c r="K71" s="47" t="inlineStr">
         <is>
-          <t>200: 수정된 사용자 정보</t>
+          <t>200: OK</t>
         </is>
       </c>
       <c r="L71" s="47" t="n"/>
@@ -6692,7 +6706,7 @@
       </c>
       <c r="B72" s="45" t="inlineStr">
         <is>
-          <t>api/v1/user-challenges</t>
+          <t>api/v1/users/me</t>
         </is>
       </c>
       <c r="C72" s="44" t="inlineStr">
@@ -6702,7 +6716,7 @@
       </c>
       <c r="D72" s="44" t="inlineStr">
         <is>
-          <t>내 챌린지 목록</t>
+          <t>내 정보 조회</t>
         </is>
       </c>
       <c r="E72" s="46" t="inlineStr">
@@ -6717,7 +6731,7 @@
       <c r="J72" s="45" t="n"/>
       <c r="K72" s="47" t="inlineStr">
         <is>
-          <t>200: {"total": int, "items": [UserChallenge]}</t>
+          <t>200: {"id": int, "email": str, "name": str, ...}</t>
         </is>
       </c>
       <c r="L72" s="47" t="n"/>
@@ -6743,17 +6757,17 @@
       </c>
       <c r="B73" s="45" t="inlineStr">
         <is>
-          <t>api/v1/challenges</t>
+          <t>api/v1/users/me</t>
         </is>
       </c>
       <c r="C73" s="44" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="D73" s="44" t="inlineStr">
         <is>
-          <t>챌린지 카탈로그 조회 (그룹별)</t>
+          <t>내 정보 수정</t>
         </is>
       </c>
       <c r="E73" s="46" t="inlineStr">
@@ -6768,7 +6782,7 @@
       <c r="J73" s="45" t="n"/>
       <c r="K73" s="47" t="inlineStr">
         <is>
-          <t>200: {"total": int, "items": [Challenge]}</t>
+          <t>200: 수정된 사용자 정보</t>
         </is>
       </c>
       <c r="L73" s="47" t="n"/>
@@ -6794,7 +6808,7 @@
       </c>
       <c r="B74" s="45" t="inlineStr">
         <is>
-          <t>api/v1/lifestyle-surveys</t>
+          <t>api/v1/user-challenges</t>
         </is>
       </c>
       <c r="C74" s="44" t="inlineStr">
@@ -6804,7 +6818,7 @@
       </c>
       <c r="D74" s="44" t="inlineStr">
         <is>
-          <t>생활습관 설문 이력</t>
+          <t>내 챌린지 목록</t>
         </is>
       </c>
       <c r="E74" s="46" t="inlineStr">
@@ -6819,7 +6833,7 @@
       <c r="J74" s="45" t="n"/>
       <c r="K74" s="47" t="inlineStr">
         <is>
-          <t>200: {"total": int, "items": [LifestyleSurvey]}</t>
+          <t>200: {"total": int, "items": [UserChallenge]}</t>
         </is>
       </c>
       <c r="L74" s="47" t="n"/>
@@ -6845,7 +6859,7 @@
       </c>
       <c r="B75" s="45" t="inlineStr">
         <is>
-          <t>api/v1/lifestyle-surveys/{id}</t>
+          <t>api/v1/challenges</t>
         </is>
       </c>
       <c r="C75" s="44" t="inlineStr">
@@ -6855,7 +6869,7 @@
       </c>
       <c r="D75" s="44" t="inlineStr">
         <is>
-          <t>생활습관 설문 단건 조회</t>
+          <t>챌린지 카탈로그 조회 (그룹별)</t>
         </is>
       </c>
       <c r="E75" s="46" t="inlineStr">
@@ -6870,7 +6884,7 @@
       <c r="J75" s="45" t="n"/>
       <c r="K75" s="47" t="inlineStr">
         <is>
-          <t>200: LifestyleSurveyResponse</t>
+          <t>200: {"total": int, "items": [Challenge]}</t>
         </is>
       </c>
       <c r="L75" s="47" t="n"/>
@@ -6896,7 +6910,7 @@
       </c>
       <c r="B76" s="45" t="inlineStr">
         <is>
-          <t>api/v1/diet-surveys</t>
+          <t>api/v1/lifestyle-surveys</t>
         </is>
       </c>
       <c r="C76" s="44" t="inlineStr">
@@ -6906,7 +6920,7 @@
       </c>
       <c r="D76" s="44" t="inlineStr">
         <is>
-          <t>식이 설문 이력</t>
+          <t>생활습관 설문 이력</t>
         </is>
       </c>
       <c r="E76" s="46" t="inlineStr">
@@ -6921,7 +6935,7 @@
       <c r="J76" s="45" t="n"/>
       <c r="K76" s="47" t="inlineStr">
         <is>
-          <t>200: {"total": int, "items": [DietSurvey]}</t>
+          <t>200: {"total": int, "items": [LifestyleSurvey]}</t>
         </is>
       </c>
       <c r="L76" s="47" t="n"/>
@@ -6947,17 +6961,17 @@
       </c>
       <c r="B77" s="45" t="inlineStr">
         <is>
-          <t>api/v1/notifications/read-all</t>
+          <t>api/v1/lifestyle-surveys/{id}</t>
         </is>
       </c>
       <c r="C77" s="44" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="D77" s="44" t="inlineStr">
         <is>
-          <t>알림 전체 읽음 처리</t>
+          <t>생활습관 설문 단건 조회</t>
         </is>
       </c>
       <c r="E77" s="46" t="inlineStr">
@@ -6972,7 +6986,7 @@
       <c r="J77" s="45" t="n"/>
       <c r="K77" s="47" t="inlineStr">
         <is>
-          <t>200: {"updated": int}</t>
+          <t>200: LifestyleSurveyResponse</t>
         </is>
       </c>
       <c r="L77" s="47" t="n"/>
@@ -6985,6 +6999,108 @@
       </c>
       <c r="P77" s="45" t="n"/>
       <c r="Q77" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B78" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/diet-surveys</t>
+        </is>
+      </c>
+      <c r="C78" s="44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D78" s="44" t="inlineStr">
+        <is>
+          <t>식이 설문 이력</t>
+        </is>
+      </c>
+      <c r="E78" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F78" s="46" t="n"/>
+      <c r="G78" s="46" t="n"/>
+      <c r="H78" s="46" t="n"/>
+      <c r="I78" s="45" t="n"/>
+      <c r="J78" s="45" t="n"/>
+      <c r="K78" s="47" t="inlineStr">
+        <is>
+          <t>200: {"total": int, "items": [DietSurvey]}</t>
+        </is>
+      </c>
+      <c r="L78" s="47" t="n"/>
+      <c r="M78" s="47" t="n"/>
+      <c r="N78" s="47" t="n"/>
+      <c r="O78" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P78" s="45" t="n"/>
+      <c r="Q78" s="44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="44" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B79" s="45" t="inlineStr">
+        <is>
+          <t>api/v1/notifications/read-all</t>
+        </is>
+      </c>
+      <c r="C79" s="44" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="D79" s="44" t="inlineStr">
+        <is>
+          <t>알림 전체 읽음 처리</t>
+        </is>
+      </c>
+      <c r="E79" s="46" t="inlineStr">
+        <is>
+          <t>{"Authorization": "Bearer &lt;token&gt;"}</t>
+        </is>
+      </c>
+      <c r="F79" s="46" t="n"/>
+      <c r="G79" s="46" t="n"/>
+      <c r="H79" s="46" t="n"/>
+      <c r="I79" s="45" t="n"/>
+      <c r="J79" s="45" t="n"/>
+      <c r="K79" s="47" t="inlineStr">
+        <is>
+          <t>200: {"updated": int}</t>
+        </is>
+      </c>
+      <c r="L79" s="47" t="n"/>
+      <c r="M79" s="47" t="n"/>
+      <c r="N79" s="47" t="n"/>
+      <c r="O79" s="45" t="inlineStr">
+        <is>
+          <t>{200, 401}</t>
+        </is>
+      </c>
+      <c r="P79" s="45" t="n"/>
+      <c r="Q79" s="44" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
